--- a/InputData/Department/Department.xlsx
+++ b/InputData/Department/Department.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\fusion-hcm-migration-mvp\InputData\Department\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1218D9F-52EE-4A03-95FE-02711413957F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C99A0A23-6BED-44BE-A5C6-7D53C9B8131F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Organization" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="74">
   <si>
     <t>SourceSystemOwner</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>PU8_CLASS</t>
+  </si>
+  <si>
+    <t>FUSION</t>
   </si>
 </sst>
 </file>
@@ -581,17 +584,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -611,7 +614,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -628,7 +631,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -645,7 +648,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -662,7 +665,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -679,7 +682,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -696,7 +699,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -713,7 +716,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -730,7 +733,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -759,9 +762,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +793,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -816,7 +819,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -842,7 +845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -868,7 +871,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -894,7 +897,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -920,7 +923,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -946,7 +949,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -972,7 +975,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1010,9 +1013,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1038,9 +1051,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -1061,9 +1074,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
@@ -1084,9 +1097,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
@@ -1107,9 +1120,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
@@ -1130,9 +1143,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
         <v>69</v>
@@ -1153,9 +1166,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
         <v>70</v>
@@ -1176,9 +1189,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
@@ -1199,9 +1212,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
